--- a/AAII_Financials/Yearly/CMS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CMS_YR_FIN.xlsx
@@ -1251,7 +1251,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-25000</v>
+        <v>-34000</v>
       </c>
       <c r="E20" s="3">
         <v>-33000</v>
@@ -1302,7 +1302,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3244000</v>
+        <v>3253000</v>
       </c>
       <c r="E21" s="3">
         <v>2929000</v>
@@ -1353,7 +1353,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>800000</v>
+        <v>809000</v>
       </c>
       <c r="E22" s="3">
         <v>726000</v>
@@ -1863,7 +1863,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>25000</v>
+        <v>34000</v>
       </c>
       <c r="E32" s="3">
         <v>33000</v>
